--- a/astro-site/public/dl/kit-tareas-pizzeria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/01-apertura-cierre.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura Cocina" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Apertura Sala" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cierre Cocina" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cierre Sala" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Cocina" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Sala" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Cocina" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Sala" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Apertura Cocina'!$A$1:$G$35</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Apertura Sala'!$A$1:$G$27</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Cierre Cocina'!$A$1:$G$31</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Cierre Sala'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cierre Cocina'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Sala'!$A$1:$G$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,11 @@
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -137,44 +142,60 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -534,15 +555,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -550,6 +572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -557,6 +580,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -585,6 +609,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -592,8 +617,33 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pizzeria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -607,16 +657,16 @@
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist de Apertura — Cocina / Obrador</t>
@@ -630,10 +680,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -658,7 +709,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -675,10 +726,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -704,10 +753,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -733,10 +780,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -762,10 +807,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -791,10 +834,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -827,10 +868,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -856,10 +895,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -885,10 +922,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -914,10 +949,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -943,10 +976,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -972,10 +1003,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -1001,10 +1030,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>12</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -1030,10 +1057,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>13</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1066,10 +1091,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="19" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -1095,10 +1118,8 @@
       <c r="G21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="18" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
@@ -1124,10 +1145,8 @@
       <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="19" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
@@ -1153,10 +1172,8 @@
       <c r="G23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="18" t="n">
+        <v>17</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
@@ -1182,10 +1199,8 @@
       <c r="G24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="19" t="n">
+        <v>18</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
@@ -1218,10 +1233,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="19" t="n">
+        <v>19</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
@@ -1247,10 +1260,8 @@
       <c r="G27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="18" t="n">
+        <v>20</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
@@ -1276,10 +1287,8 @@
       <c r="G28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="19" t="n">
+        <v>21</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
@@ -1304,6 +1313,7 @@
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="14" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="C31" s="15" t="inlineStr">
         <is>
@@ -1312,14 +1322,19 @@
       </c>
       <c r="D31" s="16">
         <f>COUNTIF(F5:F29,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>de 21</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F31">
+        <f>COUNTIF(B5:B29,"?*")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -1327,6 +1342,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
@@ -1345,7 +1361,17 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G29">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1360,16 +1386,16 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist de Apertura — Sala y Terraza</t>
@@ -1383,10 +1409,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1411,7 +1438,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1428,10 +1455,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1457,10 +1482,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1486,10 +1509,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1515,10 +1536,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1544,10 +1563,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -1573,10 +1590,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -1602,10 +1617,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -1638,10 +1651,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -1667,10 +1678,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -1696,10 +1705,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -1732,10 +1739,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -1761,10 +1766,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1790,10 +1793,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -1819,10 +1820,8 @@
       <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="19" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -1847,6 +1846,7 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="14" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="15" t="inlineStr">
         <is>
@@ -1855,14 +1855,19 @@
       </c>
       <c r="D23" s="16">
         <f>COUNTIF(F5:F21,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>de 14</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F23">
+        <f>COUNTIF(B5:B21,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -1870,6 +1875,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
@@ -1882,12 +1888,22 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A13:G13"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1902,16 +1918,16 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist de Cierre — Cocina / Obrador</t>
@@ -1925,10 +1941,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1953,7 +1970,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1970,10 +1987,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1999,10 +2014,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -2028,10 +2041,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -2057,10 +2068,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -2086,10 +2095,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -2122,10 +2129,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -2151,10 +2156,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -2180,10 +2183,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -2209,10 +2210,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -2245,10 +2244,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -2274,10 +2271,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -2303,10 +2298,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -2332,10 +2325,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -2361,10 +2352,8 @@
       <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="19" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -2397,10 +2386,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="19" t="n">
+        <v>15</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
@@ -2426,10 +2413,8 @@
       <c r="G23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="18" t="n">
+        <v>16</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
@@ -2455,10 +2440,8 @@
       <c r="G24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="19" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
@@ -2483,6 +2466,7 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="14" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="C27" s="15" t="inlineStr">
         <is>
@@ -2491,14 +2475,19 @@
       </c>
       <c r="D27" s="16">
         <f>COUNTIF(F5:F25,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>de 17</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F27">
+        <f>COUNTIF(B5:B25,"?*")</f>
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
@@ -2506,6 +2495,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
@@ -2524,7 +2514,17 @@
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -2539,16 +2539,16 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist de Cierre — Sala, Terraza y Delivery</t>
@@ -2562,10 +2562,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2590,7 +2591,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -2607,10 +2608,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -2636,10 +2635,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -2665,10 +2662,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -2694,10 +2689,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -2730,10 +2723,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -2759,10 +2750,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -2795,10 +2784,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -2824,10 +2811,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -2853,10 +2838,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -2882,10 +2865,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -2911,10 +2892,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -2940,10 +2919,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -2976,10 +2953,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="19" t="n">
+        <v>13</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -3005,10 +2980,8 @@
       <c r="G21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="18" t="n">
+        <v>14</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
@@ -3033,6 +3006,7 @@
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="10" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="C24" s="15" t="inlineStr">
         <is>
@@ -3041,14 +3015,19 @@
       </c>
       <c r="D24" s="16">
         <f>COUNTIF(F5:F22,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>de 14</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F24">
+        <f>COUNTIF(B5:B22,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -3056,6 +3035,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
@@ -3074,7 +3054,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F14 F15 F16 F17 F18 F19 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pizzeria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/01-apertura-cierre.xlsx
@@ -14,9 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Sala" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Cocina'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Apertura Sala'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cierre Cocina'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cierre Cocina'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cierre Sala'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Sala'!$A$1:$G$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -652,7 +656,7 @@
   <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1371,8 +1375,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1381,7 +1393,7 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1903,8 +1915,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1913,7 +1933,7 @@
   <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2524,8 +2544,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2534,7 +2562,7 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3064,7 +3092,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pizzeria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/01-apertura-cierre.xlsx
@@ -14,14 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Sala" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Cocina'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Apertura Sala'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cierre Cocina'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cierre Cocina'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cierre Cocina'!$A$1:$G$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cierre Sala'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Sala'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Sala'!$A$1:$G$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,8 +90,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +136,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -148,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +204,49 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,79 +624,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Tareas de Apertura y Cierre — Pizzería</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Checklists diarios para abrir y cerrar cada área de tu pizzería.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Imprime una copia por día y área</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• El responsable marca las tareas completadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>• El encargado firma al final de cada turno</t>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>• Personaliza: borra lo que no aplique, añade lo tuyo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="B9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = tarea pendiente · ✓ = completada (escribe en columna 'Hecha')</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
         </is>
       </c>
     </row>
     <row r="14"/>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pizzeria · info@aichef.pro</t>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>▸ Estás en 01-apertura-cierre.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pizzeria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -658,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -723,655 +874,983 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HIGIENE PERSONAL</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Uniforme y calzado de trabajo limpios, delantal cambiado y pelo recogido (gorro o redecilla)</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Sin anillos, reloj ni pulseras; uñas cortas, limpias y sin esmalte: la masa se estira a mano</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Heridas y cortes cubiertos con apósito impermeable de color visible y guante encima</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Lavado de manos al entrar y en cada cambio de tarea; lavamanos con jabón, papel y agua caliente</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Declarar síntomas digestivos o respiratorios: quien los tenga no manipula alimentos</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Pizzero</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  HORNO</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Encender la campana extractora y ventilar la cocina ANTES de encender el horno: la leña y el gas necesitan tiro desde el primer minuto</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Pizzero</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Comprobar el tiro de la chimenea y que la trampilla del horno de leña está abierta antes de prender nada</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Pizzero</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Abrir la llave general de gas y comprobar que NO huele a gas; si huele, no enciendas nada, ventila y avisa al mantenedor</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Pizzero</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Encender horno de leña/piedra (precalentar 45-60 min)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Verificar temperatura del horno (400-450°C para napolitana)</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>Verificar temperatura del horno (400-450 °C para napolitana)</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>10:45</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Preparar leña/pellets si es horno de leña</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Limpiar piedra del horno con cepillo de latón</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Encender horno de pastas/gratinados si aplica</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  MASA Y MISE EN PLACE</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="24" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Comprobar que las cámaras han funcionado toda la noche y registrar temperatura (refrigeración 0-4 °C / congelación ≤ −18 °C) — anota la lectura: ____ °C. Si hay desviación, no uses la masa ni el género hasta valorarlo</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Cámara</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Pizzero</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Sacar bolas de masa de cámara (temperar 1-2h)</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Verificar estado de la masa: fermentación, textura, burbujas</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Preparar masa fresca si no hay suficiente del día anterior</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>Preparar salsa de tomate del día (si es casera)</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E25" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Cortar mozzarella fresca y escurrir</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Preparar toppings: pepperoni, jamón, champiñones, aceitunas</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E27" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Preparar vegetales: rúcula, tomate fresco, cebolla, pimiento</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Preparar vegetales: rúcula, tomate fresco, cebolla, pimiento — los de consumo crudo (rúcula, albahaca, tomate) se lavan y desinfectan con lejía apta para uso alimentario a la dosis del fabricante y se ACLARAN con agua potable abundante</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>Montar línea de montaje: masa → salsa → queso → toppings</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  STOCK Y VERIFICACIONES</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>Verificar stock de harina (00, integral)</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C31" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Verificar stock de mozzarella y quesos</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>Verificar stock de tomate (lata/fresco)</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C33" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Preparar lista de pedidos urgentes</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Verificar caducidades de productos abiertos</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C35" s="27" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D35" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E35" s="27" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HIGIENE</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Lavarse manos y colocarse uniforme</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="28" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HIGIENE PRE-SERVICIO</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>Lavarse las manos al volver del reparto o después de manejar dinero, cajas o basura, ANTES de volver a tocar la masa</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="28" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>Desinfectar superficies de trabajo y mesa de amasado</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D38" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
         <is>
           <t>Verificar jabón y papel en dispensadores</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D31" s="16">
-        <f>COUNTIF(F5:F29,"✓")</f>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="n"/>
+      <c r="B40" s="32" t="n"/>
+      <c r="C40" s="27" t="n"/>
+      <c r="D40" s="27" t="n"/>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="n"/>
+      <c r="B41" s="32" t="n"/>
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="28" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="n"/>
+      <c r="B42" s="32" t="n"/>
+      <c r="C42" s="27" t="n"/>
+      <c r="D42" s="27" t="n"/>
+      <c r="E42" s="27" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="27" t="n"/>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="n"/>
+      <c r="B44" s="32" t="n"/>
+      <c r="C44" s="27" t="n"/>
+      <c r="D44" s="27" t="n"/>
+      <c r="E44" s="27" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D46" s="16">
+        <f>COUNTIFS(B5:B44,"?*",F5:F44,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F31">
-        <f>COUNTIF(B5:B29,"?*")</f>
-        <v>21.0</v>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="F46">
+        <f>COUNTIF(B5:B44,"?*")-COUNTIF(F5:F44,"N/A")</f>
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Pizzería · AI Chef Pro · aichef.pro —</t>
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="10">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A46:C46"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G29">
+  <conditionalFormatting sqref="A5:G44">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F26 F27 F28 F29 F31 F32 F33 F34 F35 F37 F38 F39 F40 F41 F42 F43 F44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1395,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1460,458 +1939,523 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Encender luces y climatización</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Limpiar y montar mesas</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Colocar menús/cartas en mesas</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Actualizar pizarra: pizza del día, especiales</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Poner música ambiental</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Verificar TPV/datáfono funcionando</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Preparar fondo de caja</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  TERRAZA</t>
         </is>
       </c>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Sacar mesas y sillas de terraza</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Limpiar mesas de terraza</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Abrir sombrillas si hace sol</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  DELIVERY / TAKE-AWAY</t>
         </is>
       </c>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Encender tablets de delivery (Glovo, Uber Eats, Just Eat)</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Verificar stock de cajas de pizza (medianas, grandes, familiares)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Verificar stock de bolsas, servilletas, salsas en sobre</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Actualizar menú en apps si hay cambios</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
     <row r="23">
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D23" s="16">
-        <f>COUNTIF(F5:F21,"✓")</f>
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="16">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F23">
-        <f>COUNTIF(B5:B21,"?*")</f>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
         <v>14.0</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Pizzería · AI Chef Pro · aichef.pro —</t>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G21">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1935,7 +2479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2000,547 +2544,645 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  MASA Y PRODUCTO</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Guardar bolas de masa sobrantes en cámara (etiquetar fecha)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Cubrir y refrigerar salsa de tomate</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Guardar mozzarella en su líquido, tapar</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Cubrir y refrigerar todos los toppings</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Etiquetar todo con fecha</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  HORNO Y EQUIPOS</t>
         </is>
       </c>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Dejar enfriar horno (no apagar de golpe si es de leña)</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Retirar ceniza del horno cuando esté frío</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Limpiar piedra del horno con cepillo</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Apagar campana extractora</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA</t>
         </is>
       </c>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Limpiar mesa de amasado y enharinar ligeramente</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Limpiar línea de montaje y bandejas</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Fregar utensilios: pala, cortapizza, rodillos</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Barrer y fregar suelo de cocina</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Sacar basura y reciclar (cartón de cajas)</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PREPARACIÓN MAÑANA</t>
         </is>
       </c>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="n">
+      <c r="A23" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Preparar masa para mañana (amasado nocturno, fermentación lenta)</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Pizzero</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Anotar faltantes para pedido</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="n">
+      <c r="A25" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Anotar las mermas del día (producto, cantidad y motivo): bolas de masa pasadas, pizzas devueltas o mal montadas y toppings retirados — sin este dato el food cost del mes sale mal</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>Pizzero</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Descongelar lo necesario para mañana</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-    </row>
-    <row r="26"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
     <row r="27">
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D27" s="16">
-        <f>COUNTIF(F5:F25,"✓")</f>
+      <c r="A27" s="31" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n"/>
+      <c r="B28" s="32" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n"/>
+      <c r="B29" s="32" t="n"/>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n"/>
+      <c r="B30" s="32" t="n"/>
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="28" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="n"/>
+      <c r="B31" s="32" t="n"/>
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="27" t="n"/>
+      <c r="E31" s="27" t="n"/>
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D33" s="16">
+        <f>COUNTIFS(B5:B31,"?*",F5:F31,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F27">
-        <f>COUNTIF(B5:B25,"?*")</f>
-        <v>17.0</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="F33">
+        <f>COUNTIF(B5:B31,"?*")-COUNTIF(F5:F31,"N/A")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Pizzería · AI Chef Pro · aichef.pro —</t>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G25">
+  <conditionalFormatting sqref="A5:G31">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21 F23 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2564,7 +3206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2629,466 +3271,537 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Desmontar mesas</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Limpiar mesas con desinfectante</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Barrer y fregar suelo</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Reponer servilletas y condimentos para mañana</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  TERRAZA</t>
         </is>
       </c>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Recoger mesas y sillas (o encadenar)</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Cerrar sombrillas</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  DELIVERY Y CAJA</t>
         </is>
       </c>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Apagar tablets de delivery</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Contar cajas de pizza restantes para mañana</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Cuadrar caja del día</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Anotar incidencias</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Apagar luces, climatización, música</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Activar alarma y cerrar</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  BAÑOS</t>
         </is>
       </c>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Limpieza final de baños</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Reponer jabón y papel</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-    </row>
-    <row r="23"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
     <row r="24">
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D24" s="16">
-        <f>COUNTIF(F5:F22,"✓")</f>
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D29" s="16">
+        <f>COUNTIFS(B5:B27,"?*",F5:F27,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F24">
-        <f>COUNTIF(B5:B22,"?*")</f>
+      <c r="F29">
+        <f>COUNTIF(B5:B27,"?*")-COUNTIF(F5:F27,"N/A")</f>
         <v>14.0</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Pizzería · AI Chef Pro · aichef.pro —</t>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Pizzería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G22">
+  <conditionalFormatting sqref="A5:G27">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F14 F15 F16 F17 F18 F19 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F14 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
